--- a/config/Excel/Skills.xlsx
+++ b/config/Excel/Skills.xlsx
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">傷害範圍</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">說明文字</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">基礎fx(JSON)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">里程碑fx(JSON)</t>
         </is>
@@ -103,17 +108,17 @@
       <c r="H2">
         <v>6</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">蓄力揮出沉重的一擊。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":360,"per":80}</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"stunDur":0.5},"8":{"stunDur":1,"critBonus":15}}</t>
         </is>
@@ -149,17 +154,17 @@
       <c r="H3">
         <v>8</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">快速的兩段斬擊。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":210,"per":44,"hits":2}</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"hits":3},"8":{"hits":3,"healPctOfDmg":12}}</t>
         </is>
@@ -197,15 +202,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t xml:space="preserve">旋轉身軀橫掃周遭。</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":505,"per":110}</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"slowDur":2},"8":{"slowDur":3,"debuff":{"key":"defDown","base":10,"per":2,"dur":4}}}</t>
         </is>
@@ -241,17 +251,17 @@
       <c r="H5">
         <v>12</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">重擊敵人的護甲弱點。</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":300,"per":60,"debuff":{"key":"defDown","base":25,"per":5,"dur":5}}</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"debuff":{"key":"defDown","base":35,"per":6,"dur":6}},"8":{"debuff":{"key":"defDown","base":45,"per":7,"dur":8},"stunDur":0.5}}</t>
         </is>
@@ -287,17 +297,17 @@
       <c r="H6">
         <v>15</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">對瀕死敵人給予終結。</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":500,"per":110,"execBelow":30,"execMult":2}</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"execBelow":40},"8":{"execBelow":50,"execMult":2.5}}</t>
         </is>
@@ -333,17 +343,17 @@
       <c r="H7">
         <v>10</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">造成難以癒合的傷口。</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":240,"per":50,"dot":{"pct":25,"dur":5,"name":"流血"}}</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dot":{"pct":40,"dur":6,"name":"流血"}},"8":{"dot":{"pct":55,"dur":7,"name":"流血"},"healPctOfDmg":15}}</t>
         </is>
@@ -379,17 +389,17 @@
       <c r="H8">
         <v>14</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">猛擊敵人使其暈眩。</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":320,"per":65,"stunDur":1.5}</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"stunDur":2},"8":{"stunDur":2.5,"debuff":{"key":"atkDown","base":10,"per":2,"dur":4}}}</t>
         </is>
@@ -425,17 +435,17 @@
       <c r="H9">
         <v>12</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">不顧自身安危的猛攻。</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":840,"per":170,"selfDmgPct":5}</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"critBonus":20},"8":{"selfDmgPct":3,"critBonus":35}}</t>
         </is>
@@ -471,17 +481,17 @@
       <c r="H10">
         <v>8</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">絕不落空的致命突刺。</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":300,"per":65,"neverMiss":true,"critBonus":30}</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"critBonus":50},"8":{"critBonus":50,"execBelow":25,"execMult":1.8}}</t>
         </is>
@@ -517,17 +527,17 @@
       <c r="H11">
         <v>13</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">沉重的壓制性打擊。</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":600,"per":130,"slowDur":3}</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"slowDur":4},"8":{"slowDur":4,"stunDur":1}}</t>
         </is>
@@ -565,15 +575,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">化作疾風的三段斬。</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":165,"per":35,"hits":3}</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"hits":4},"8":{"hits":5,"dot":{"pct":15,"dur":3,"name":"流血"}}}</t>
         </is>
@@ -609,17 +624,17 @@
       <c r="H13">
         <v>18</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">擺出以牙還牙的架勢。</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"thornsUp","base":12,"per":4,"dur":6}}</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buff2":{"key":"blockUp","base":10,"per":3,"dur":6}},"8":{"buff":{"key":"thornsUp","base":20,"per":6,"dur":8}}}</t>
         </is>
@@ -655,17 +670,17 @@
       <c r="H14">
         <v>12</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">三連斬光落下，將敵人的魂魄烙上戰印。</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":145,"per":32,"hits":3,"brand":{"name":"魂痕","storePct":30,"dur":8,"maxStacks":3}}</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"brand":{"name":"魂痕","storePct":30,"dur":8,"maxStacks":5}},"8":{"brand":{"name":"魂痕","storePct":45,"dur":10,"maxStacks":5}}}</t>
         </is>
@@ -701,17 +716,17 @@
       <c r="H15">
         <v>16</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">一擊定罪，引爆所有烙印的宿命。</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":560,"per":110,"detonate":{"brand":"any","multPct":{"base":120,"per":3},"resetCd":{"id":"soulBrandFlurry","pct":25}}}</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"detonate":{"brand":"any","multPct":{"base":120,"per":3},"stunDur":1,"resetCd":{"id":"soulBrandFlurry","pct":25}}},"8":{"detonate":{"brand":"any","multPct":{"base":150,"per":3},"stunDur":1,"resetCd":{"id":"soulBrandFlurry","pct":40}}}}</t>
         </is>
@@ -749,15 +764,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">2*2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">斬擊的殘影在剎那之後追上真實。</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":520,"per":100,"dmgWindow":{"dur":2,"pct":35}}</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dmgWindow":{"dur":2,"pct":50}},"8":{"dmgWindow":{"dur":3,"pct":50}}}</t>
         </is>
@@ -793,17 +813,17 @@
       <c r="H17">
         <v>5</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">鬥氣隨戰意輪轉，蓄滿之刻便是爆發之時。</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">{"charge":{"name":"鬥氣","add":1,"max":3,"dur":15,"source":"attackHit","burst":{"multPct":{"base":120,"per":5},"scope":"next"}}}</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"charge":{"name":"鬥氣","add":1,"addCrit":2,"max":3,"dur":15,"source":"attackHit","burst":{"multPct":{"base":120,"per":5},"scope":"next"}}},"8":{"charge":{"name":"鬥氣","add":1,"addCrit":2,"max":3,"dur":15,"source":"attackHit","burst":{"multPct":{"base":150,"per":5},"scope":"next","keepStacks":1}}}}</t>
         </is>
@@ -839,17 +859,17 @@
       <c r="H18">
         <v>14</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">號令一出，萬刃爭先。</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">{"cdShift":{"scope":"cat:phys","sec":{"base":1.5,"per":0.1}}}</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"cdShift":{"sec":{"base":1.5,"per":0.1}}},"8":{"cdShift":{"sec":{"base":1.5,"per":0.1},"extraPct":10}}}</t>
         </is>
@@ -885,17 +905,17 @@
       <c r="H19">
         <v>16</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">先聲奪人，為最沉重的一擊鋪路。</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">{"skillAmp":{"scope":"next","dur":8,"uses":1,"perCdSec":{"base":4,"per":0.1},"cap":120}}</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"skillAmp":{"scope":"next","dur":8,"uses":2,"perCdSec":{"base":4,"per":0.1},"cap":120}},"8":{"skillAmp":{"scope":"next","dur":8,"uses":2,"perCdSec":{"base":4,"per":0.1},"cap":120,"cdrPct":20,"cdrMinCd":15}}}</t>
         </is>
@@ -931,17 +951,17 @@
       <c r="H20">
         <v>12</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">讓所有傷口在同一瞬間崩裂。</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dotPulse":{"ticks":2,"powerPct":{"base":100,"per":3}},"requiresTargetDot":true}</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dotPulse":{"ticks":3,"powerPct":{"base":100,"per":3}}},"8":{"dotPulse":{"ticks":3,"powerPct":{"base":100,"per":3}},"dotHaste":{"mult":2,"dur":3}}}</t>
         </is>
@@ -977,17 +997,17 @@
       <c r="H21">
         <v>15</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">招式相連，戰意不絕。</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">{"comboWindow":{"dur":3,"pct":{"base":25,"per":1}}}</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"comboWindow":{"dur":4,"pct":{"base":25,"per":1}}},"8":{"comboWindow":{"dur":4,"pct":{"base":25,"per":1},"noGcd":true}}}</t>
         </is>
@@ -1023,17 +1043,17 @@
       <c r="H22">
         <v>18</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">千鋒出鞘，方圓皆為劍之領域。</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":220,"per":45,"field":{"name":"劍域","dur":6,"tickSec":1,"tickPct":25}}</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"field":{"name":"劍域","dur":6,"tickSec":1,"tickPct":25,"takenAmpPct":10}},"8":{"field":{"name":"劍域","dur":6,"tickSec":0.6,"tickPct":25,"takenAmpPct":10}}}</t>
         </is>
@@ -1074,17 +1094,17 @@
       <c r="H23">
         <v>10</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">釋放純粹的奧術能量。</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":330,"per":75}</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"mpOnCrit":15},"8":{"mpOnCrit":15,"doubleCastPct":15}}</t>
         </is>
@@ -1125,17 +1145,17 @@
       <c r="H24">
         <v>9</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">投出灼熱的火球並點燃敵人。</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":360,"per":80,"dot":{"pct":20,"dur":4,"name":"燃燒"}}</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dot":{"pct":35,"dur":5,"name":"燃燒"}},"8":{"dot":{"pct":45,"dur":6,"name":"燃燒"}}}</t>
         </is>
@@ -1178,15 +1198,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">1*3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">冰冷的長槍刺穿敵人。</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":330,"per":70,"slowDur":3}</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"slowDur":4},"8":{"slowDur":4,"stunDur":0.8}}</t>
         </is>
@@ -1227,17 +1252,17 @@
       <c r="H26">
         <v>11</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">躍動的閃電連續劈落。</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":190,"per":40,"hits":2}</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"hits":3},"8":{"hits":3,"doubleCastPct":20}}</t>
         </is>
@@ -1278,17 +1303,17 @@
       <c r="H27">
         <v>12</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">瀰漫的毒霧侵蝕敵人。</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":200,"per":40,"dot":{"pct":40,"dur":6,"name":"中毒"}}</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dot":{"pct":55,"dur":7,"name":"中毒"}},"8":{"dot":{"pct":65,"dur":8,"name":"中毒"},"debuff":{"key":"atkDown","base":12,"per":2,"dur":5}}}</t>
         </is>
@@ -1329,17 +1354,17 @@
       <c r="H28">
         <v>10</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">聖光降下裁決並潔淨己身。</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":340,"per":70,"selfCleanse":true}</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"healPctMax":{"base":4,"per":1}},"8":{"healPctMax":{"base":6,"per":1.5},"buff":{"key":"atkUp","base":8,"per":2,"dur":5}}}</t>
         </is>
@@ -1380,17 +1405,17 @@
       <c r="H29">
         <v>10</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">汲取生命的暗影之矢。</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":320,"per":70,"healPctOfDmg":30}</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"healPctOfDmg":45},"8":{"healPctOfDmg":55,"dot":{"pct":25,"dur":4,"name":"侵蝕"}}}</t>
         </is>
@@ -1431,17 +1456,17 @@
       <c r="H30">
         <v>15</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">傾瀉四發奧術飛彈。</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":135,"per":30,"hits":4}</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"hits":5},"8":{"hits":6,"mpOnCrit":10}}</t>
         </is>
@@ -1484,15 +1509,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">呼喚天降隕石毀滅一切。</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":1260,"per":255}</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dot":{"pct":30,"dur":5,"name":"燃燒"}},"8":{"dot":{"pct":40,"dur":6,"name":"燃燒"},"stunDur":1.2}}</t>
         </is>
@@ -1533,17 +1563,17 @@
       <c r="H32">
         <v>8</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t xml:space="preserve">以法力引發劇烈爆燃，爆擊時返還法力。</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":320,"per":70,"mpOnCrit":20}</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"mpOnCrit":35},"8":{"mpOnCrit":40,"debuff":{"key":"defDown","base":15,"per":3,"dur":5}}}</t>
         </is>
@@ -1584,17 +1614,17 @@
       <c r="H33">
         <v>14</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">迸發的冰環凍結敵人。</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":260,"per":55,"stunDur":1}</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"stunDur":1.5},"8":{"stunDur":1.5,"slowDur":4}}</t>
         </is>
@@ -1635,17 +1665,17 @@
       <c r="H34">
         <v>18</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">撕開無視一切防禦的虛空。</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"true","stat":"matk","base":325,"per":70}</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"execBelow":30,"execMult":1.5},"8":{"execBelow":30,"execMult":1.5,"doubleCastPct":15}}</t>
         </is>
@@ -1686,17 +1716,17 @@
       <c r="H35">
         <v>9</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">雷紋入體，蓄勢待鳴。</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":260,"per":55,"brand":{"name":"雷印","storePct":35,"dur":8,"maxStacks":1}}</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"brand":{"name":"雷印","storePct":35,"dur":8,"maxStacks":2}},"8":{"brand":{"name":"雷印","storePct":45,"dur":12,"maxStacks":3}}}</t>
         </is>
@@ -1737,17 +1767,17 @@
       <c r="H36">
         <v>12</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">碎印之刻，湮滅隨行。</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":300,"per":65,"detonate":{"brand":"any","multPct":{"base":150,"per":3},"chainPct":60}}</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"detonate":{"brand":"any","multPct":{"base":200,"per":3},"chainPct":60,"stunDur":0.8}},"8":{"detonate":{"brand":"any","multPct":{"base":200,"per":3},"chainPct":60,"stunDur":0.8,"healPctMaxPerStack":4}}}</t>
         </is>
@@ -1790,15 +1820,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">燼焰未熄，烈火再臨。</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":330,"per":70,"echo":{"delay":2,"powerPct":40,"repeat":1}}</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"echo":{"delay":2,"powerPct":60,"repeat":1}},"8":{"echo":{"delay":2,"powerPct":60,"repeat":2}}}</t>
         </is>
@@ -1839,17 +1874,17 @@
       <c r="H38">
         <v>20</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">焚世之火，燎盡八荒。</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":240,"per":50,"field":{"name":"焚世領域","dur":6,"tickSec":1,"tickPct":25,"elem":"fire","takenAmpPct":15}}</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"field":{"name":"焚世領域","dur":8,"tickSec":1,"tickPct":25,"elem":"fire","takenAmpPct":15}},"8":{"field":{"name":"焚世領域","dur":8,"tickSec":0.8,"tickPct":35,"elem":"fire","takenAmpPct":15}}}</t>
         </is>
@@ -1890,17 +1925,17 @@
       <c r="H39">
         <v>14</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">讓蔓延的疫病在一瞬間齊聲炸裂。</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":200,"per":42,"dotDetonate":{"pct":{"base":80,"per":1},"cap":100},"dot":{"pct":40,"dur":6,"name":"瘟疫"},"requiresTargetDot":true}</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dotDetonate":{"pct":{"base":80,"per":1},"cap":100,"stunDur":0.8}},"8":{"dotDetonate":{"pct":{"base":80,"per":1},"cap":100,"stunDur":0.8,"reapplyPct":40}}}</t>
         </is>
@@ -1941,17 +1976,17 @@
       <c r="H40">
         <v>8</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t xml:space="preserve">霜晶共鳴，凜冬將至。</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":240,"per":50,"charge":{"name":"霜晶","add":1,"max":4,"dur":20,"source":"cast","burst":{"multPct":180,"scope":"self"}}}</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"charge":{"name":"霜晶","add":2,"max":4,"dur":20,"source":"cast","burst":{"multPct":180,"scope":"self"}}},"8":{"charge":{"name":"霜晶","add":2,"max":4,"dur":20,"source":"cast","burst":{"multPct":260,"scope":"self","stunDur":1.2}}}}</t>
         </is>
@@ -1992,17 +2027,17 @@
       <c r="H41">
         <v>15</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t xml:space="preserve">引導星辰之力，注入下一式。</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">{"skillAmp":{"scope":"next","pct":{"base":30,"per":3},"dur":8,"uses":1,"refundPct":40}}</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"skillAmp":{"scope":"next","pct":{"base":30,"per":3},"dur":8,"uses":2,"refundPct":40}},"8":{"skillAmp":{"scope":"next","pct":{"base":30,"per":3},"dur":8,"uses":2,"refundPct":40,"cdrPct":30}}}</t>
         </is>
@@ -2043,17 +2078,17 @@
       <c r="H42">
         <v>16</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">以血為潮，掀起狂濤。</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":300,"per":65,"hpSacrifice":{"hpPct":15,"ampPct":{"base":80,"per":2}}}</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"hpSacrifice":{"hpPct":15,"ampPct":{"base":80,"per":2},"hotRefundPct":50,"hotDur":6}},"8":{"hpSacrifice":{"hpPct":15,"ampPct":{"base":80,"per":2},"hotRefundPct":50,"hotDur":6,"dmgToShieldPct":15}}}</t>
         </is>
@@ -2094,17 +2129,17 @@
       <c r="H43">
         <v>12</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t xml:space="preserve">凜冬迴潮，捲回流逝的時間。</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":260,"per":55,"cdShift":{"sec":{"base":1.5,"per":0.1}}}</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"cdResetOnKill":{"pct":30,"selfReset":true,"icdSec":3}},"8":{"cdShift":{"sec":{"base":2.5,"per":0.1}},"cdResetOnKill":{"pct":30,"selfReset":true,"icdSec":3},"cdResetOnKill2":{"othersPct":20,"icdSec":3}}}</t>
         </is>
@@ -2145,17 +2180,17 @@
           <t xml:space="preserve">hurt70</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t xml:space="preserve">溫暖的光輝癒合傷口。</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">{"healPctMax":{"base":15,"per":4}}</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"selfCleanse":true},"8":{"buff":{"key":"defUp","base":15,"per":3,"dur":4}}}</t>
         </is>
@@ -2196,17 +2231,17 @@
           <t xml:space="preserve">hurt80</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">持續再生的自然之力。</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">{"hotPct":{"base":2.5,"per":0.7},"hotDur":6}</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"hotDur":8},"8":{"hotPct":{"base":4,"per":1},"hotDur":8}}</t>
         </is>
@@ -2247,17 +2282,17 @@
           <t xml:space="preserve">shield</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t xml:space="preserve">展開吸收傷害的屏障。</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">{"shieldPctMax":{"base":18,"per":4}}</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"shieldPctMax":{"base":24,"per":5}},"8":{"shieldPctMax":{"base":28,"per":6},"buff":{"key":"blockUp","base":10,"per":2,"dur":6}}}</t>
         </is>
@@ -2298,17 +2333,17 @@
           <t xml:space="preserve">hurt50</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">硬化全身抵禦攻擊。</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"defUp","base":40,"per":10,"dur":6}}</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buff2":{"key":"thornsUp","base":8,"per":2,"dur":6}},"8":{"buff":{"key":"defUp","base":55,"per":12,"dur":8}}}</t>
         </is>
@@ -2349,17 +2384,17 @@
           <t xml:space="preserve">debuffed</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">洗去身上的負面狀態。</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">{"selfCleanse":true,"healPctMax":{"base":5,"per":1.5}}</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"healPctMax":{"base":8,"per":2}},"8":{"buff":{"key":"evasionUp","base":15,"per":3,"dur":3}}}</t>
         </is>
@@ -2400,17 +2435,17 @@
       <c r="H49">
         <v>10</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">奪取敵人的生命力。</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":220,"per":50,"healPctOfDmg":100}</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"healPctOfDmg":130},"8":{"healPctOfDmg":150,"dot":{"pct":30,"dur":4,"name":"侵蝕"}}}</t>
         </is>
@@ -2451,17 +2486,17 @@
           <t xml:space="preserve">hurt40</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t xml:space="preserve">神聖領域護佑己身。</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"evasionUp","base":25,"per":5,"dur":5}}</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buff2":{"key":"defUp","base":15,"per":3,"dur":5}},"8":{"buff":{"key":"evasionUp","base":35,"per":6,"dur":6}}}</t>
         </is>
@@ -2502,17 +2537,17 @@
           <t xml:space="preserve">hurt30</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t xml:space="preserve">危急時的求生本能（不耗魔）。</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">{"healPctMax":{"base":10,"per":3},"mpRestore":20}</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"mpRestore":40},"8":{"mpRestore":50,"healPctMax":{"base":16,"per":4}}}</t>
         </is>
@@ -2548,17 +2583,17 @@
       <c r="H52">
         <v>18</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t xml:space="preserve">反彈傷害的光盾。</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"thornsUp","base":15,"per":5,"dur":6},"buff2":{"key":"blockUp","base":12,"per":4,"dur":6}}</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"shieldPctMax":{"base":8,"per":2}},"8":{"buff":{"key":"thornsUp","base":25,"per":6,"dur":8}}}</t>
         </is>
@@ -2599,17 +2634,17 @@
           <t xml:space="preserve">hurt25</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t xml:space="preserve">絕境中爆發的鬥志。</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">{"healPctMax":{"base":20,"per":5},"buff":{"key":"atkUp","base":15,"per":5,"dur":6}}</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buff2":{"key":"aspdUp","base":15,"per":3,"dur":6}},"8":{"healPctMax":{"base":30,"per":6}}}</t>
         </is>
@@ -2650,17 +2685,17 @@
       <c r="H54">
         <v>14</v>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">聖盾崩華之瞬，守護化為鋒芒。</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":180,"per":40,"shieldBurst":{"convertPct":60,"capAtkMult":10}}</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"shieldBurst":{"convertPct":85,"capAtkMult":10}},"8":{"shieldBurst":{"convertPct":85,"capAtkMult":10,"stunDur":1}}}</t>
         </is>
@@ -2701,17 +2736,17 @@
       <c r="H55">
         <v>16</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">滿溢的聖光，即是裁罰。</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">{"healPctMax":{"base":12,"per":3},"overhealDmg":{"pct":{"base":40,"per":2},"cap":90}}</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"overhealDmg":{"pct":{"base":40,"per":2},"cap":90,"windowSec":6}},"8":{"overhealDmg":{"pct":{"base":70,"per":2},"cap":90,"windowSec":6}}}</t>
         </is>
@@ -2752,17 +2787,17 @@
       <c r="H56">
         <v>9</v>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t xml:space="preserve">承受的苦難，終將輪迴為裁決。</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":200,"per":45,"stigma":{"storePct":35,"dur":8,"capMaxHpPct":20,"multPct":130}}</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"stigma":{"storePct":35,"dur":8,"capMaxHpPct":35,"multPct":130}},"8":{"stigma":{"storePct":35,"dur":8,"capMaxHpPct":35,"multPct":130,"shieldPct":130,"stunDur":1}}}</t>
         </is>
@@ -2803,17 +2838,17 @@
       <c r="H57">
         <v>12</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t xml:space="preserve">傷痛的回響，化作汲魂的甘露。</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":200,"per":45,"healPctOfDmg":60,"healEcho":{"dur":2,"pct":{"base":40,"per":2}}}</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"healEcho":{"dur":2,"pct":{"base":60,"per":2}}},"8":{"healEcho":{"dur":4,"pct":{"base":60,"per":2}}}}</t>
         </is>
@@ -2854,17 +2889,17 @@
       <c r="H58">
         <v>18</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t xml:space="preserve">聖言連禱，為守護者開路。</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">{"healPctMax":{"base":6,"per":1.5},"freeNext":{"count":1,"dur":6,"scope":"cat:def","ampPct":{"base":30,"per":2}}}</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"freeNext":{"count":2,"dur":6,"scope":"cat:def","ampPct":{"base":30,"per":2}}},"8":{"freeNext":{"count":2,"dur":6,"scope":"cat:def","ampPct":{"base":30,"per":2},"cdHalf":true}}}</t>
         </is>
@@ -2905,17 +2940,17 @@
       <c r="H59">
         <v>15</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t xml:space="preserve">聖詠不歇，恩澤長存。</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">{"healPctMax":{"base":5,"per":1.2},"buffExtend":{"sec":2}}</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buffExtend":{"sec":3}},"8":{"buffExtend":{"sec":3},"buffExtend2":{"sec":3}}}</t>
         </is>
@@ -2956,17 +2991,17 @@
           <t xml:space="preserve">shield</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t xml:space="preserve">壁壘每一次震響，都是反攻的號角。</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">{"shieldPctMax":{"base":10,"per":2.5},"cdOnHitTaken":{"sec":0.4,"icdSec":0.5}}</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"cdOnHitTaken":{"sec":0.6,"icdSec":0.5}},"8":{"cdOnHitTaken":{"sec":0.6,"icdSec":0.5,"onBreak":2}}}</t>
         </is>
@@ -3002,17 +3037,17 @@
       <c r="H61">
         <v>7</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t xml:space="preserve">承受吧——怒火終將百倍奉還。</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":140,"per":30,"charge":{"name":"蓄怒","add":1,"max":4,"dur":15,"source":"hitTaken","burst":{"multPct":{"base":200,"per":6},"scope":"self"}}}</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"charge":{"name":"蓄怒","add":1,"addBlock":2,"max":4,"dur":15,"source":"hitTaken","burst":{"multPct":{"base":200,"per":6},"scope":"self"}}},"8":{"charge":{"name":"蓄怒","add":1,"addBlock":2,"max":4,"dur":15,"source":"hitTaken","burst":{"multPct":{"base":200,"per":6},"scope":"self","anyMultPct":60}}}}</t>
         </is>
@@ -3053,17 +3088,17 @@
       <c r="H62">
         <v>22</v>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">受聖化的禱言，讓守護亦能傷人。</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">{"healPctMax":{"base":8,"per":2},"skillAmp":{"scope":"cat:def","pct":{"base":20,"per":4},"dur":8}}</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"skillAmp":{"scope":"cat:def","pct":{"base":20,"per":4},"dur":10}},"8":{"skillAmp":{"scope":"all","pct":{"base":20,"per":4},"dur":10}}}</t>
         </is>
@@ -3099,17 +3134,17 @@
       <c r="H63">
         <v>20</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t xml:space="preserve">加速自身的時間流。</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"aspdUp","base":25,"per":7,"dur":6}}</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{},"8":{"buff":{"key":"aspdUp","base":40,"per":9,"dur":7}}}</t>
         </is>
@@ -3145,17 +3180,17 @@
       <c r="H64">
         <v>20</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t xml:space="preserve">揮出將敵人化為財富的一擊。</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":200,"per":40,"goldPer":15}</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"goldPer":25},"8":{"goldPer":35,"buff":{"key":"lootUp","base":15,"per":3,"dur":5}}}</t>
         </is>
@@ -3191,17 +3226,17 @@
       <c r="H65">
         <v>30</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t xml:space="preserve">嗅出寶物的氣息。</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"lootUp","base":15,"per":5,"dur":10}}</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buff":{"key":"lootUp","base":22.5,"per":6,"dur":12}},"8":{"goldPer":5}}</t>
         </is>
@@ -3242,17 +3277,17 @@
       <c r="H66">
         <v>15</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">削弱敵人的力量。</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">{"debuff":{"key":"atkDown","base":18,"per":4,"dur":6}}</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"slowDur":2},"8":{"debuff":{"key":"atkDown","base":28,"per":5,"dur":8}}}</t>
         </is>
@@ -3293,17 +3328,17 @@
       <c r="H67">
         <v>20</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">以敵人生命為薪的詛咒。</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">{"maxHpDotPct":{"base":2.4,"per":0.8},"dotDur":5}</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dotDur":7},"8":{"maxHpDotPct":{"base":1.8,"per":0.5},"dotDur":7}}</t>
         </is>
@@ -3339,17 +3374,17 @@
       <c r="H68">
         <v>16</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t xml:space="preserve">殘影閃避致命攻擊。</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"evasionUp","base":35,"per":7,"dur":3}}</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buff":{"key":"evasionUp","base":45,"per":8,"dur":4}},"8":{}}</t>
         </is>
@@ -3390,17 +3425,17 @@
       <c r="H69">
         <v>12</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">從敵人身上抽取法力（不耗魔）。</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":160,"per":30,"mpRestore":25}</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"mpRestore":40},"8":{"mpRestore":45,"debuff":{"key":"atkDown","base":10,"per":2,"dur":4}}}</t>
         </is>
@@ -3436,17 +3471,17 @@
       <c r="H70">
         <v>22</v>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">讓每次爆擊更加致命。</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"critDmgUp","base":40,"per":12,"dur":6}}</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{},"8":{"buff":{"key":"critDmgUp","base":60,"per":15,"dur":8}}}</t>
         </is>
@@ -3482,17 +3517,17 @@
       <c r="H71">
         <v>18</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t xml:space="preserve">震天的吼聲鼓舞自己、震懾敵人。</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buff":{"key":"atkUp","base":12,"per":4,"dur":6},"debuff":{"key":"atkDown","base":8,"per":2,"dur":6}}</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"debuff":{"key":"atkDown","base":12,"per":3,"dur":6}},"8":{"buff":{"key":"atkUp","base":18,"per":5,"dur":8}}}</t>
         </is>
@@ -3528,17 +3563,17 @@
       <c r="H72">
         <v>15</v>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t xml:space="preserve">傷害在 50%~250% 之間隨機。</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":375,"per":85,"gamble":true}</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"critBonus":20},"8":{"critBonus":20,"execBelow":35,"execMult":2}}</t>
         </is>
@@ -3579,17 +3614,17 @@
       <c r="H73">
         <v>18</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t xml:space="preserve">命運的輪盤，永遠轉向出乎意料的一格。</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":180,"per":35,"proc":{"on":"hit","pct":100,"do":"castRandom","powerPct":{"base":50,"per":2}}}</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"proc":{"on":"hit","pct":100,"do":"castRandom","powerPct":{"base":70,"per":2}}},"8":{"proc":{"on":"hit","pct":100,"do":"castRandom","powerPct":{"base":70,"per":2}},"proc2":{"on":"hit","pct":35,"do":"castRandom","powerPct":{"base":70,"per":2}}}}</t>
         </is>
@@ -3630,17 +3665,17 @@
       <c r="H74">
         <v>14</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t xml:space="preserve">昔日的輝煌，此刻重演。</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":300,"per":60,"replayBest":{"powerPct":{"base":40,"per":2},"window":6,"repeat":1}}</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"replayBest":{"powerPct":{"base":40,"per":2},"window":6,"repeat":2}},"8":{"replayBest":{"powerPct":{"base":65,"per":2},"window":10,"repeat":2}}}</t>
         </is>
@@ -3681,17 +3716,17 @@
       <c r="H75">
         <v>20</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t xml:space="preserve">竊走的每一秒，都屬於最漫長的等待。</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":200,"per":40,"cdShift":{"sec":{"base":3,"per":0.2},"focus":"longest"}}</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"cdShift":{"sec":{"base":3,"per":0.2},"focus":"longest","onKillRepeat":{"icdSec":2}}},"8":{"cdShift":{"sec":{"base":3,"per":0.2},"focus":"longest","onKillRepeat":{"icdSec":2},"zeroSelfCdrPct":50}}}</t>
         </is>
@@ -3727,17 +3762,17 @@
       <c r="H76">
         <v>8</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t xml:space="preserve">籌碼疊滿之時，就是梭哈之刻。</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":150,"per":30,"charge":{"name":"籌碼","addRange":[1,3],"max":5,"dur":15,"source":"cast","burst":{"multPct":{"base":150,"per":4},"scope":"next"}}}</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"charge":{"name":"籌碼","addRange":[2,4],"max":5,"dur":15,"source":"cast","burst":{"multPct":{"base":150,"per":4},"scope":"next"}}},"8":{"charge":{"name":"籌碼","addRange":[2,4],"max":5,"dur":20,"source":"cast","burst":{"multPct":{"base":180,"per":4},"scope":"next"}}}}</t>
         </is>
@@ -3778,17 +3813,17 @@
       <c r="H77">
         <v>12</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t xml:space="preserve">萬象歸一印，一印破萬象。</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":220,"per":45,"detonate":{"brand":"any","multPct":{"base":200,"per":5}},"brand":{"name":"萬象印","storePct":35,"dur":10,"maxStacks":1}}</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"brand":{"name":"萬象印","storePct":35,"dur":10,"maxStacks":2}},"8":{"brand":{"name":"萬象印","storePct":35,"dur":10,"maxStacks":2},"detonate":{"brand":"any","multPct":{"base":200,"per":5},"stunDur":1,"healPctMax":3}}}</t>
         </is>
@@ -3829,17 +3864,17 @@
       <c r="H78">
         <v>25</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t xml:space="preserve">傾盡所有法力，換一擊無悔（不耗魔）。</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">{"dmgType":"magic","stat":"matk","base":250,"per":50,"mpDump":{"pctPer10Mp":{"base":2,"per":0.15}}}</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"mpDump":{"pctPer10Mp":{"base":3,"per":0.15}}},"8":{"mpDump":{"pctPer10Mp":{"base":3,"per":0.15}},"freeNext":{"count":1,"dur":6}}}</t>
         </is>
@@ -3875,17 +3910,17 @@
       <c r="H79">
         <v>22</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t xml:space="preserve">心流湧動之間，施法再無滯礙。</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">{"freeNext":{"count":2,"dur":{"base":5,"per":0.3}}}</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"freeNext":{"count":2,"dur":{"base":5,"per":0.3},"noGcd":true}},"8":{"freeNext":{"count":4,"dur":{"base":5,"per":0.3},"noGcd":true}}}</t>
         </is>
@@ -3921,17 +3956,17 @@
       <c r="H80">
         <v>15</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t xml:space="preserve">連段共鳴，段段生威。</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">{"skillAmp":{"scope":"multiHit","pct":{"base":35,"per":4},"dur":10}}</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"skillAmp":{"scope":"multiHit","pct":{"base":35,"per":4},"dur":14}},"8":{"skillAmp":{"scope":"multiHit","pct":{"base":35,"per":4},"dur":14},"skillAmp2":{"scope":"next","pct":30,"uses":1}}}</t>
         </is>
@@ -3967,17 +4002,17 @@
       <c r="H81">
         <v>16</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t xml:space="preserve">拋下時之錨，讓美好的瞬間多留一會。</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">{"buffExtend":{"sec":{"base":1.5,"per":0.15}}}</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"buffExtend2":{"sec":1.5}},"8":{"buffExtend":{"sec":{"base":3,"per":0.15}},"buffExtend2":{"sec":1.5}}}</t>
         </is>
@@ -4007,12 +4042,12 @@
           <t xml:space="preserve">🪨</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t xml:space="preserve">生命上限提升。</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"hpPct":5}}</t>
         </is>
@@ -4042,12 +4077,12 @@
           <t xml:space="preserve">⚔️</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t xml:space="preserve">物理攻擊提升。</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"atkPct":4}}</t>
         </is>
@@ -4082,12 +4117,12 @@
           <t xml:space="preserve">🧠</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">魔法攻擊提升。</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"matkPct":4}}</t>
         </is>
@@ -4117,12 +4152,12 @@
           <t xml:space="preserve">💨</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t xml:space="preserve">攻擊速度提升。</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"aspdPct":2}}</t>
         </is>
@@ -4152,12 +4187,12 @@
           <t xml:space="preserve">👁️</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t xml:space="preserve">暴擊率提升。</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"critRate":2}}</t>
         </is>
@@ -4187,12 +4222,12 @@
           <t xml:space="preserve">💢</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t xml:space="preserve">暴擊傷害提升。</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"critDmg":8}}</t>
         </is>
@@ -4222,12 +4257,12 @@
           <t xml:space="preserve">🧛</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t xml:space="preserve">吸血提升。</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"lifesteal":1.5}}</t>
         </is>
@@ -4257,12 +4292,12 @@
           <t xml:space="preserve">🧘</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t xml:space="preserve">法力上限與回復提升。</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"mpFlat":20,"mpRegen":1}}</t>
         </is>
@@ -4292,12 +4327,12 @@
           <t xml:space="preserve">🛡️</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t xml:space="preserve">物理與魔法防禦提升。</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"defPct":5,"mdefPct":5}}</t>
         </is>
@@ -4327,12 +4362,12 @@
           <t xml:space="preserve">🍀</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t xml:space="preserve">金幣與經驗獲取提升。</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passive":{"goldBonus":5,"xpBonus":5}}</t>
         </is>
@@ -4362,17 +4397,17 @@
           <t xml:space="preserve">🔁</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t xml:space="preserve">每一次出手，都可能留下殘響。</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveEcho":{"pct":{"base":15,"per":1},"powerPct":30,"delay":2}}</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveEcho":{"pct":{"base":15,"per":1},"powerPct":45,"delay":2}},"8":{"passiveEcho":{"pct":{"base":15,"per":1},"powerPct":45,"delay":2,"secondPct":25,"secondPowerPct":50}}}</t>
         </is>
@@ -4402,17 +4437,17 @@
           <t xml:space="preserve">🪦</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t xml:space="preserve">死神的節拍，催促下一次收割。</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveKillCd":{"sec":{"base":1,"per":0.05},"icdSec":2}}</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveKillCd":{"sec":{"base":1,"per":0.05},"icdSec":2,"selfResetPct":15}},"8":{"passiveKillCd":{"sec":{"base":1,"per":0.05},"icdSec":2,"selfResetPct":15,"inclBasic":true}}}</t>
         </is>
@@ -4442,17 +4477,17 @@
           <t xml:space="preserve">🥷</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t xml:space="preserve">殺意所至，身隨影動。</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveProc":{"on":"crit","pct":{"base":20,"per":1},"do":"freeAttack"}}</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveProc":{"on":"crit","pct":{"base":20,"per":1},"do":"freeAttack","forceCrit":true}},"8":{"passiveProc":{"on":"crit","pct":{"base":20,"per":1},"do":"freeAttack","forceCrit":true,"recastPct":20,"recastPowerPct":40}}}</t>
         </is>
@@ -4487,17 +4522,17 @@
           <t xml:space="preserve">🧫</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t xml:space="preserve">讓毒與傷以更急促的頻率侵蝕。</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveDotHaste":{"mult":{"base":1.2,"per":0.02}}}</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"dotAmpPer":6},"8":{"dotAmpPer":6,"dotSplashOnKill":50}}</t>
         </is>
@@ -4527,17 +4562,17 @@
           <t xml:space="preserve">🧿</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t xml:space="preserve">歸零的節律，醞釀免費的爆發。</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveNthFree":{"n":5,"ampPct":{"base":40,"per":4}}}</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveNthFree":{"n":4,"ampPct":{"base":40,"per":4}}},"8":{"passiveNthFree":{"n":4,"ampPct":{"base":40,"per":4},"noGcd":true}}}</t>
         </is>
@@ -4567,17 +4602,17 @@
           <t xml:space="preserve">👥</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t xml:space="preserve">連斬之後，幻影仍在追擊。</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveExtraHit":{"minHits":2,"powerPct":{"base":30,"per":2},"count":1}}</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveExtraHit":{"minHits":2,"powerPct":{"base":30,"per":2},"count":1,"neverMiss":true}},"8":{"passiveExtraHit":{"minHits":2,"powerPct":{"base":30,"per":2},"count":2,"neverMiss":true}}}</t>
         </is>
@@ -4607,17 +4642,17 @@
           <t xml:space="preserve">⚙️</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t xml:space="preserve">最堅實的防守，孕育最銳利的反擊。</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveDefFeedback":{"pct":{"base":25,"per":3},"stacks":1}}</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveDefFeedback":{"pct":{"base":25,"per":3},"stacks":2}},"8":{"passiveDefFeedback":{"pct":{"base":25,"per":3},"stacks":2,"cdRefund":2}}}</t>
         </is>
@@ -4647,17 +4682,17 @@
           <t xml:space="preserve">🏹</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t xml:space="preserve">獵人的烙印，永不輕易褪去。</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveBrandAmp":{"storeBonus":{"base":20,"per":1},"keepPct":25}}</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveBrandAmp":{"storeBonus":{"base":20,"per":1},"keepPct":40}},"8":{"passiveBrandAmp":{"storeBonus":{"base":20,"per":1},"keepPct":40,"transferOnKill":true}}}</t>
         </is>
@@ -4687,17 +4722,17 @@
           <t xml:space="preserve">🕯️</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t xml:space="preserve">流光不滅，恩澤永續。</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">{"passiveCastExtend":{"sec":{"base":0.4,"per":0.05}}}</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">{"4":{"passiveCastExtend":{"sec":{"base":0.4,"per":0.05},"alsoDots":0.5}},"8":{"passiveCastExtend":{"sec":{"base":0.4,"per":0.05},"alsoDots":0.5,"lowThreshold2x":true}}}</t>
         </is>
@@ -4730,12 +4765,12 @@
       <c r="H101">
         <v>60</v>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t xml:space="preserve">突破速度極限，攻速掙脫 5 次/秒的枷鎖，能達到什麼程度端看你的領悟。</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":0,"per":5,"dur":6,"mech":"aspd","en":"Velocity Force","desc":"在 6 秒內突破速度極限——你的攻速在此刻可以突破 5 次/秒的限制、直抵無限，至於能達到什麼程度，得看你的領悟了。每級 +5% 攻速加成。"}</t>
         </is>
@@ -4773,12 +4808,12 @@
       <c r="H102">
         <v>45</v>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t xml:space="preserve">過載的雷能在敵群間肆意跳躍，愈是激烈愈難止息。</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":100,"per":5,"atkBase":70000,"atkPer":4000,"bounces":5,"dur":8,"dmgType":"magic","mech":"chainLightning","en":"Lightning Overdrive","desc":"雷霆過載，萬雷臨世——凝聚過載雷能轟落敵陣，造成大量電屬性魔法傷害並於敵群間彈跳撕裂，持續時間內每一秒皆再度轟落；其間雷能縈繞不散，雷電傷害大幅提升，雷電技能命中更引動連鎖雷鏈，愈戰愈烈、生生不息。"}</t>
         </is>
@@ -4811,12 +4846,12 @@
       <c r="H103">
         <v>75</v>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t xml:space="preserve">此技能對自身冷卻不生效，但冷卻縮減仍可作用於它。</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":0,"per":0.2,"dur":3,"mech":"cdrUncap","en":"Chronostasis","desc":"打破時空的禁錮——冷卻縮減自此突破 60% 的天塹，所有技能的冷卻如坍縮的星辰般急速消融，持續 3 秒。每級額外 −0.2% 冷卻。（不縮減自身冷卻，但仍受一般冷卻縮減加成）"}</t>
         </is>
@@ -4849,12 +4884,12 @@
       <c r="H104">
         <v>75</v>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t xml:space="preserve">在絕對的領域中，任何傷害都無法觸及你分毫。</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":0.5,"per":0.025,"mech":"invuln","en":"Absolute Sanctuary","desc":"降臨絕對的領域，展開無敵結界——其間免疫一切傷害與負面效果，任何攻擊都無法觸及你分毫。基礎 0.5 秒，每級 +0.025 秒。"}</t>
         </is>
@@ -4887,12 +4922,12 @@
       <c r="H105">
         <v>90</v>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t xml:space="preserve">意志不屈者，縱使命懸一線也絕不倒下。（此技能不受冷卻縮減影響）</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"passiveTrigger","base":0,"per":0.4,"mech":"undyingGuard","en":"Last Undying Stand","desc":"意志不屈者，縱使命懸一線亦絕不倒下——受到致命傷害時免除死亡，並獲得 1 秒無敵。觸發後進入冷卻，每級 −0.4 秒。（不受冷卻縮減影響）"}</t>
         </is>
@@ -4925,12 +4960,12 @@
       <c r="H106">
         <v>45</v>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t xml:space="preserve">結界之內，敵人的時間被無情拖曳。</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":0,"per":1,"dur":8,"mech":"enemySlow","en":"Time Barrier","desc":"編織拖曳時光的結界，敵人的動作被無情延緩，攻速大幅降低，持續 8 秒。每級敵人攻速 −1%。（敵降低後攻速 = 原攻速 /(1+降低%)）"}</t>
         </is>
@@ -4960,12 +4995,12 @@
           <t xml:space="preserve">☯️</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t xml:space="preserve">雙核交融，物理與魔法在你手中不再涇渭分明。</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"passive","base":0,"per":0.6,"mech":"crossCore","en":"Dual-Core Fusion","desc":"雙核交融，物理與魔法的界限就此崩解——所有物理技能汲取魔攻之力、所有魔法技能承載物攻之威。每級 +0.6%。"}</t>
         </is>
@@ -4998,12 +5033,12 @@
       <c r="H108">
         <v>60</v>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t xml:space="preserve">爆擊率愈高，這一擊便愈是毀天滅地。</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":100,"per":3,"dmgType":"phys","mech":"omega","en":"Omega Impact","desc":"凝聚全身之力於一擊，依你的爆擊率轟出毀天滅地的必殺——造成「爆擊率% × 必殺傷害加成%」的物理傷害；爆擊率愈高，此擊愈是無可匹敵。必殺傷害加成 = 100% + 每級 +3%。"}</t>
         </is>
@@ -5041,12 +5076,12 @@
       <c r="H109">
         <v>45</v>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t xml:space="preserve">滿溢的聖光既能療癒自身，亦能化為裁決敵人的利刃。</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":0,"per":0.5,"dur":6,"mech":"sacredInvert","en":"Sacred Inversion","desc":"聖療之光賜福於身，生命與法力回復大幅提升；滿溢的療癒之力逆轉為裁決，化作同等傷害傾瀉於敵，持續 6 秒。每級 +0.5%。"}</t>
         </is>
@@ -5079,12 +5114,12 @@
       <c r="H110">
         <v>120</v>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t xml:space="preserve">唯有獲得神之賜福者，方能在凝滯的時空中行動自如。</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">{"type":"active","base":40,"per":0.5,"dur":8,"mech":"timeStop","en":"Chronos Stasis","desc":"封鎖周遭的時空，令萬物靜止——唯有承神之賜福者能自由行動；凝滯之間你的所有傷害大幅提升，敵人動彈不得，持續 8 秒。每級 +0.5% 所有傷害。"}</t>
         </is>
@@ -5634,33 +5669,90 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">里程碑fx(JSON)</t>
+          <t xml:space="preserve">傷害範圍</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">格式：{"等級":{覆蓋欄位},…}，例 {"4":{…},"8":{…}}；</t>
+          <t xml:space="preserve">空白＝單體(1*1)，一次只打 1 個敵人；</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">＝技能升到該等級後，用其中欄位「覆蓋」基礎fx的同名欄位(淺層覆蓋、達標的高等級優先)；</t>
+          <t xml:space="preserve">A*B＝直向 A 格 × 橫向 B 格，以主目標為準取該大小的方框，框內敵人全部命中；</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">可用變量與定義同上「基礎fx(JSON)」；</t>
+          <t xml:space="preserve">　例：3*3 方框、2*2 方框、1*3 由左往右貫穿的直線、3*1 擋在面前的橫牆；</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all＝全體：對敵方 4×4 棋盤內所有敵人造成傷害；</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主目標的挑法與普攻相同（最近優先、同距離隨機、鎖定不換）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">佔多格的單位(BOSS)被範圍蓋到時仍只算命中 1 次；</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外觸發的傷害(引爆／濺射／連鎖)不受此欄影響，也不算進單體/群體判定；</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">里程碑fx(JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">格式：{"等級":{覆蓋欄位},…}，例 {"4":{…},"8":{…}}；</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">＝技能升到該等級後，用其中欄位「覆蓋」基礎fx的同名欄位(淺層覆蓋、達標的高等級優先)；</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可用變量與定義同上「基礎fx(JSON)」；</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力技能不使用此欄；</t>
         </is>

--- a/config/Excel/Skills.xlsx
+++ b/config/Excel/Skills.xlsx
@@ -217,7 +217,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"4":{"slowDur":2},"8":{"slowDur":3,"debuff":{"key":"defDown","base":10,"per":2,"dur":4}}}</t>
+          <t xml:space="preserve">{"4":{"slowDur":2},"8":{"slowDur":3,"buff":{"key":"penUp","base":10,"per":2,"dur":4}}}</t>
         </is>
       </c>
     </row>
@@ -258,12 +258,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":300,"per":60,"debuff":{"key":"defDown","base":25,"per":5,"dur":5}}</t>
+          <t xml:space="preserve">{"dmgType":"phys","stat":"atk","base":300,"per":60,"buff":{"key":"penUp","base":25,"per":5,"dur":5}}</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"4":{"debuff":{"key":"defDown","base":35,"per":6,"dur":6}},"8":{"debuff":{"key":"defDown","base":45,"per":7,"dur":8},"stunDur":0.5}}</t>
+          <t xml:space="preserve">{"4":{"buff":{"key":"penUp","base":35,"per":6,"dur":6}},"8":{"buff":{"key":"penUp","base":45,"per":7,"dur":8},"stunDur":0.5}}</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"4":{"mpOnCrit":35},"8":{"mpOnCrit":40,"debuff":{"key":"defDown","base":15,"per":3,"dur":5}}}</t>
+          <t xml:space="preserve">{"4":{"mpOnCrit":35},"8":{"mpOnCrit":40,"buff":{"key":"penUp","base":15,"per":3,"dur":5}}}</t>
         </is>
       </c>
     </row>
@@ -5514,245 +5514,259 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">key種類：atkUp=攻擊/defUp=防禦/aspdUp=攻速/evasionUp=閃避/critDmgUp=爆傷/lootUp=掉寶/thornsUp=反震/blockUp=格擋/hot=再生/atkDown=降敵攻/defDown=降敵防；</t>
+          <t xml:space="preserve">key種類：atkUp=攻擊/defUp=防禦/aspdUp=攻速/evasionUp=閃避/critDmgUp=爆傷/lootUp=掉寶/thornsUp=反震/blockUp=格擋/hot=再生/penUp=物理與魔法穿透/atkDown=降敵攻/defDown=降敵防；</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">【處決/其他】</t>
+          <t xml:space="preserve">注意：2026-07-30 起技能不再使用 defDown（降敵防）；原有降防技改為 buff penUp（增加自身物理與魔法穿透%）；</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">execBelow=處決閾值(敵血量%以下觸發)；</t>
+          <t xml:space="preserve">　　　defDown 僅為舊存檔融合技快照的相容保留，新設計請勿再填；</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">execMult=處決傷害倍率；</t>
+          <t xml:space="preserve">【處決/其他】</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">goldPer=金幣掠奪係數(×技能等級×角色等級)；</t>
+          <t xml:space="preserve">execBelow=處決閾值(敵血量%以下觸發)；</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">doubleCastPct=雙重施法機率%；</t>
+          <t xml:space="preserve">execMult=處決傷害倍率；</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">comboDetonate=冰火引爆追加傷害%(融合變異)；</t>
+          <t xml:space="preserve">goldPer=金幣掠奪係數(×技能等級×角色等級)；</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">【被動技】</t>
+          <t xml:space="preserve">doubleCastPct=雙重施法機率%；</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">passive={屬性:每級數值}；</t>
+          <t xml:space="preserve">comboDetonate=冰火引爆追加傷害%(融合變異)；</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">屬性種類：hpPct=生命上限%/atkPct=物攻%/matkPct=魔攻%/aspdPct=攻速%/critRate=爆擊率/critDmg=爆擊傷害/lifesteal=吸血/mpFlat=法力上限/mpRegen=法力回復每秒/defPct=物防%/mdefPct=魔防%/goldBonus=金幣獲取%/xpBonus=經驗獲取%；</t>
+          <t xml:space="preserve">【被動技】</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">【潛力技能(系統分類=potential)】</t>
+          <t xml:space="preserve">passive={屬性:每級數值}；</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">type=類型(active=主動/passive=被動/passiveTrigger=被動觸發)；</t>
+          <t xml:space="preserve">屬性種類：hpPct=生命上限%/atkPct=物攻%/matkPct=魔攻%/aspdPct=攻速%/critRate=爆擊率/critDmg=爆擊傷害/lifesteal=吸血/mpFlat=法力上限/mpRegen=法力回復每秒/defPct=物防%/mdefPct=魔防%/goldBonus=金幣獲取%/xpBonus=經驗獲取%；</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">base=效果基準值；</t>
+          <t xml:space="preserve">【潛力技能(系統分類=potential)】</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">per=每級效果增量；</t>
+          <t xml:space="preserve">type=類型(active=主動/passive=被動/passiveTrigger=被動觸發)；</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">atkBase=本體攻擊傷害%基準(雷霆過載：魔攻%)；</t>
+          <t xml:space="preserve">base=效果基準值；</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">atkPer=每級本體攻擊傷害%增量；</t>
+          <t xml:space="preserve">per=每級效果增量；</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">bounces=本體攻擊彈跳次數(每跳完整傷害)；</t>
+          <t xml:space="preserve">atkBase=本體攻擊傷害%基準(雷霆過載：魔攻%)；</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">dur=增益持續秒；</t>
+          <t xml:space="preserve">atkPer=每級本體攻擊傷害%增量；</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgType=傷害類型(phys=物理/magic=魔法)；</t>
+          <t xml:space="preserve">bounces=本體攻擊彈跳次數(每跳完整傷害)；</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">mech=戰鬥機制代號(接線鍵勿改)；</t>
+          <t xml:space="preserve">dur=增益持續秒；</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">en=英文名；</t>
+          <t xml:space="preserve">dmgType=傷害類型(phys=物理/magic=魔法)；</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">desc=質變說明(面板顯示的完整敘述)；</t>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
+          <t xml:space="preserve">mech=戰鬥機制代號(接線鍵勿改)；</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en=英文名；</t>
+        </is>
+      </c>
+    </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">傷害範圍</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">空白＝單體(1*1)，一次只打 1 個敵人；</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">desc=質變說明(面板顯示的完整敘述)；</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">A*B＝直向 A 格 × 橫向 B 格，以主目標為準取該大小的方框，框內敵人全部命中；</t>
+          <t xml:space="preserve">傷害範圍</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">　例：3*3 方框、2*2 方框、1*3 由左往右貫穿的直線、3*1 擋在面前的橫牆；</t>
+          <t xml:space="preserve">空白＝單體(1*1)，一次只打 1 個敵人；</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">all＝全體：對敵方 4×4 棋盤內所有敵人造成傷害；</t>
+          <t xml:space="preserve">A*B＝直向 A 格 × 橫向 B 格，以主目標為準取該大小的方框，框內敵人全部命中；</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">主目標的挑法與普攻相同（最近優先、同距離隨機、鎖定不換）；</t>
+          <t xml:space="preserve">　例：3*3 方框、2*2 方框、1*3 由左往右貫穿的直線、3*1 擋在面前的橫牆；</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">佔多格的單位(BOSS)被範圍蓋到時仍只算命中 1 次；</t>
+          <t xml:space="preserve">all＝全體：對敵方 4×4 棋盤內所有敵人造成傷害；</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外觸發的傷害(引爆／濺射／連鎖)不受此欄影響，也不算進單體/群體判定；</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
+          <t xml:space="preserve">主目標的挑法與普攻相同（最近優先、同距離隨機、鎖定不換）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">佔多格的單位(BOSS)被範圍蓋到時仍只算命中 1 次；</t>
+        </is>
+      </c>
+    </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">里程碑fx(JSON)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">格式：{"等級":{覆蓋欄位},…}，例 {"4":{…},"8":{…}}；</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">額外觸發的傷害(引爆／濺射／連鎖)不受此欄影響，也不算進單體/群體判定；</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">＝技能升到該等級後，用其中欄位「覆蓋」基礎fx的同名欄位(淺層覆蓋、達標的高等級優先)；</t>
+          <t xml:space="preserve">里程碑fx(JSON)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">可用變量與定義同上「基礎fx(JSON)」；</t>
+          <t xml:space="preserve">格式：{"等級":{覆蓋欄位},…}，例 {"4":{…},"8":{…}}；</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">＝技能升到該等級後，用其中欄位「覆蓋」基礎fx的同名欄位(淺層覆蓋、達標的高等級優先)；</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可用變量與定義同上「基礎fx(JSON)」；</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力技能不使用此欄；</t>
         </is>

--- a/config/Excel/Skills.xlsx
+++ b/config/Excel/Skills.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F4F18E-7559-4A49-8A1E-FF254A72E2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46122F8-BB9E-42B9-B545-D24FA8F21529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3018,6 +3018,7 @@
   <dimension ref="A1:N110"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
+    <col min="12" max="12" width="41.125" customWidth="1"/>
     <col min="14" max="14" width="60" customWidth="1"/>
   </cols>
   <sheetData>

--- a/config/Excel/Skills.xlsx
+++ b/config/Excel/Skills.xlsx
@@ -2558,12 +2558,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shieldPctMax":{"base":18,"per":4}}</t>
+          <t xml:space="preserve">{"status":[{"id":"shield","base":18,"per":4}]}</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"4":{"shieldPctMax":{"base":24,"per":5}},"8":{"shieldPctMax":{"base":28,"per":6},"status":[{"id":"blockUp","base":10,"per":2,"dur":6}]}}</t>
+          <t xml:space="preserve">{"4":{"status":[{"id":"shield","base":24,"per":5}]},"8":{"status":[{"id":"shield","base":28,"per":6},{"id":"blockUp","base":10,"per":2,"dur":6}]}}</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"4":{"shieldPctMax":{"base":8,"per":2}},"8":{"status":[{"id":"thornsUp","base":25,"per":6,"dur":8},{"id":"blockUp","base":12,"per":4,"dur":6}]}}</t>
+          <t xml:space="preserve">{"4":{"status":[{"id":"shield","base":8,"per":2},{"id":"thornsUp","base":15,"per":5,"dur":6},{"id":"blockUp","base":12,"per":4,"dur":6}]},"8":{"status":[{"id":"shield","base":8,"per":2},{"id":"thornsUp","base":25,"per":6,"dur":8},{"id":"blockUp","base":12,"per":4,"dur":6}]}}</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shieldPctMax":{"base":10,"per":2.5},"cdOnHitTaken":{"sec":0.4,"icdSec":0.5}}</t>
+          <t xml:space="preserve">{"cdOnHitTaken":{"sec":0.4,"icdSec":0.5},"status":[{"id":"shield","base":10,"per":2.5}]}</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
